--- a/data/trans_orig/IQ2605_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ2605_R2-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>61458</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>71514</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>41,58%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>35,33%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>48,38%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>65259</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>55739</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>75132</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>55319</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>74071</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>48,7%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>41,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>56,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>61458</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>52412</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>70856</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>41,58%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112191</t>
+          <t>113938</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>140648</t>
+          <t>141941</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>50,36%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>86365</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>76309</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>95595</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>58,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>51,62%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>64,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>68753</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>58880</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>78273</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>59941</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>78693</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>51,3%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>43,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>58,41%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>86365</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>76967</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>95411</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>58,42%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141187</t>
+          <t>139894</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>169644</t>
+          <t>167897</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>59,57%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>147823</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>147823</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>147823</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>134012</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>134012</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>134012</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>147823</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>147823</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>147823</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>120634</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>109096</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>132161</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>57,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>52,05%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>63,05%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>99815</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>88297</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>109495</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>88923</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>111012</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>51,8%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>45,82%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>56,83%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>120634</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>108815</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>132808</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>57,55%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>205014</t>
+          <t>204862</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>237688</t>
+          <t>235626</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>58,57%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>88967</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>77440</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>100505</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>42,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>36,95%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>47,95%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>92872</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>83192</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>104390</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>81675</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>103764</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>48,2%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>43,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>54,18%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>88967</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>76793</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>100786</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>42,45%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164600</t>
+          <t>166662</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>197274</t>
+          <t>197426</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>209601</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>209601</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>209601</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>308</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>192687</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>192687</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>192687</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>209601</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>209601</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>209601</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>65174</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>56087</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>75143</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>45,66%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39,29%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>52,65%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>67358</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>59307</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>76137</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>58798</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>76472</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>51,18%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>57,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>65174</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>56784</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>75241</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>45,66%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>120121</t>
+          <t>120735</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145424</t>
+          <t>146178</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,28%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>77561</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>67592</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>86648</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>54,34%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>47,35%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>60,71%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>64257</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>55478</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>72308</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>55143</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>72817</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>48,82%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>42,15%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>54,94%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>77561</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>67494</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>85951</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>54,34%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128926</t>
+          <t>128172</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154229</t>
+          <t>153615</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>142735</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>142735</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>142735</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>131615</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>131615</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>131615</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>142735</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>142735</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>142735</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>126136</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>114443</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>137417</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>61,09%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>55,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>66,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>126147</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>115054</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>138011</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>113695</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>138690</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>61,13%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>55,76%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>66,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>126136</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>115663</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>137730</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>61,09%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>235144</t>
+          <t>237074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>269027</t>
+          <t>269974</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,4%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>80331</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>69050</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>92024</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>33,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>44,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>80202</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>68338</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>91295</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>67659</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>92654</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>38,87%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>33,12%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>44,24%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>80331</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>68737</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>90804</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>38,91%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143789</t>
+          <t>142842</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>177672</t>
+          <t>175742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206467</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206467</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206467</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206349</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206349</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206349</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206467</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206467</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206467</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>373402</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>351905</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>393254</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>52,84%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>49,8%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>55,65%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>538</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>358579</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>336981</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>378576</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>339361</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>379085</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>53,95%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>50,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>56,96%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>373402</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>350621</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>394190</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>52,84%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>702468</t>
+          <t>702365</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>762083</t>
+          <t>760534</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,46%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>333224</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>313372</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>354721</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>47,16%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>44,35%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>50,2%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>454</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>306084</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>286087</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>327682</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>285578</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>325302</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>46,05%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>43,04%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>49,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>333224</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>312436</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>356005</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>47,16%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>609205</t>
+          <t>610754</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>668820</t>
+          <t>668923</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,78%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>706626</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>706626</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>706626</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>992</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>664663</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>664663</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>664663</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>706626</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>706626</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>706626</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>114785</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>104932</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>122897</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>77,55%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>70,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>83,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>108949</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>99795</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>116283</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>100393</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>116383</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>78,95%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>72,32%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>84,27%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>114785</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>105752</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>122852</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>77,55%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>211230</t>
+          <t>211063</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>235323</t>
+          <t>234723</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,07%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33223</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25111</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>43076</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>22,45%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,97%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>29,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>29046</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>21712</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>38200</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>21612</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>37602</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>21,05%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>27,68%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>33223</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>25156</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>42256</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>22,45%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50681</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74774</t>
+          <t>74941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148008</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148008</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148008</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>137995</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>137995</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>137995</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148008</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148008</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148008</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>168385</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>157673</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>177777</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>77,58%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>72,64%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>81,91%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>156895</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>147325</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>165373</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>147933</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>165338</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>79,18%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>74,35%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>83,45%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>168385</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>158178</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>178824</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>77,58%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>312047</t>
+          <t>309046</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>338323</t>
+          <t>338119</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,43%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>48664</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>39272</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>59376</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>22,42%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18,09%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>27,36%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>41265</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>32787</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>50835</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>32822</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>50227</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>20,82%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,55%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>25,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>48664</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>38225</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>58871</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>22,42%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76887</t>
+          <t>77091</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>103163</t>
+          <t>106164</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>217049</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>217049</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>217049</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>198160</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>198160</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>198160</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>217049</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>217049</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>217049</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>114607</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>104555</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>122851</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>72,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>66,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>77,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>103337</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>93291</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>111513</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>93755</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>111086</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>68,95%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>62,25%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>74,41%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>114607</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>105389</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>123253</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>72,35%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>204307</t>
+          <t>203826</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>230386</t>
+          <t>230493</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,77%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>43800</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>35556</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>53852</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>27,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>22,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>34,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>46532</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>38356</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>56578</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>38783</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>56114</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>31,05%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>25,59%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>37,75%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>43800</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>35154</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>53018</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>27,65%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77890</t>
+          <t>77783</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>103969</t>
+          <t>104450</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158407</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158407</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158407</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>149869</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>149869</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>149869</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158407</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158407</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158407</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>132982</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>121267</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>143865</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>66,06%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>60,24%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>71,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>137123</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>125831</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>148622</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>125126</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>148230</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>67,94%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>62,34%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>73,63%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>132982</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>121363</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>143753</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>66,06%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>251365</t>
+          <t>254016</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>285378</t>
+          <t>285754</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,88%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>68324</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>57441</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>80039</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>33,94%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>28,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>39,76%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>64721</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>53222</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>76013</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>53614</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>76718</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>32,06%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>26,37%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>37,66%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>68324</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>57553</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>79943</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>33,94%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117772</t>
+          <t>117396</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151785</t>
+          <t>149134</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201306</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201306</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201306</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>201844</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>201844</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>201844</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>201306</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>201306</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>201306</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>530759</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>511646</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>548841</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>73,23%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>70,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>75,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>733</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>506305</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>486435</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>527029</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>485730</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>525483</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>73,6%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>70,72%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>76,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>758</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>530759</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>511119</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>550397</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>73,23%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1007259</t>
+          <t>1006721</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1064264</t>
+          <t>1064836</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,38%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>194012</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>175930</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>213125</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>24,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29,41%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>181563</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>160839</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>201433</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>162385</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>202138</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>26,4%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>29,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>194012</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>174374</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>213652</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>26,77%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>348375</t>
+          <t>347803</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>405380</t>
+          <t>405918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>724771</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>724771</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>724771</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>990</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>687868</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>687868</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>687868</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1033</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>724771</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>724771</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>724771</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>115107</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>105781</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>123300</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>78,14%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>71,81%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>83,7%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>86228</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>75499</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>94758</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>76812</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>94509</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>66,23%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>57,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>72,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>115107</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>106458</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>123090</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>78,14%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>188789</t>
+          <t>187617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>215413</t>
+          <t>213486</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>76,93%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>32207</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24014</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>41533</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>21,86%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,3%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>28,19%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>43976</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>35446</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54705</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>35695</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>53392</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>33,77%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>27,22%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>42,01%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>32207</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>24224</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>40856</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>21,86%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62105</t>
+          <t>64032</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88729</t>
+          <t>89901</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>147314</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>147314</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>147314</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>130204</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>130204</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>130204</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>147314</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>147314</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>147314</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>172714</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>162023</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>182988</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>77,87%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>73,05%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>82,51%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>159059</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>149032</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>167539</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>148935</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>167187</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>77,67%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>72,77%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>81,81%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>172714</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>161935</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>181493</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>77,87%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>318101</t>
+          <t>317061</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>345483</t>
+          <t>345777</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,06%</t>
         </is>
       </c>
     </row>
@@ -5078,67 +5078,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>49076</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>38802</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>59767</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>22,13%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17,49%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>26,95%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>45730</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>37250</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>55757</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>37602</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>55854</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>22,33%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>27,23%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>49076</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>40297</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>59855</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>81096</t>
+          <t>80802</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>108478</t>
+          <t>109518</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221790</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221790</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221790</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>204789</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>204789</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>204789</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221790</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221790</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221790</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>142079</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>133700</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>147990</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>85,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>80,78%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>89,42%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>129433</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>122015</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>136005</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>122127</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>136192</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>84,9%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>80,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>89,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>142079</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>133453</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>147982</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>85,84%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>261236</t>
+          <t>260336</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>280621</t>
+          <t>280252</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,14%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23428</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>17517</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>31807</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>14,16%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10,58%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>19,22%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>23017</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16445</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>30435</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>16258</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>30323</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>15,1%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10,79%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>19,96%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>23428</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>17525</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>32054</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>14,16%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37337</t>
+          <t>37706</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56722</t>
+          <t>57622</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165507</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165507</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165507</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>152450</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>152450</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>152450</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165507</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165507</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165507</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>153876</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>141951</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>162854</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>75,91%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>70,02%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>80,33%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>151371</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>139777</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>161874</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>139361</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>160214</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>73,97%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>68,3%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>79,1%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>153876</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>143576</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>163512</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>75,91%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>289383</t>
+          <t>290147</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>320208</t>
+          <t>319092</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,33%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>48845</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>60770</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24,09%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19,67%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>29,98%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>53275</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>42772</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>64869</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>44432</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>65285</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>26,03%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20,9%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>31,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>48845</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>39209</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>59145</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>24,09%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>87159</t>
+          <t>88275</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>117984</t>
+          <t>117220</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202721</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202721</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202721</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>204646</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>204646</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>204646</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202721</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202721</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202721</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>583776</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>563535</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>600903</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>79,17%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>76,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>81,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>800</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>526091</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>507772</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>543676</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>507027</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>543833</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>76,01%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>73,37%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>78,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>837</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>583776</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>562734</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>600860</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>79,17%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1082965</t>
+          <t>1082220</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1135614</t>
+          <t>1134290</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,35%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>153556</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>136429</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>173797</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>20,83%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>23,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>165998</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>148413</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>184317</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>148256</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>185062</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>23,99%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>21,44%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>26,63%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>153556</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>136472</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>174598</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>20,83%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>293807</t>
+          <t>295131</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>346456</t>
+          <t>347201</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1041</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>692089</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>692089</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>692089</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23387</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18822</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27226</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>72,02%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>57,97%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>83,85%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>19998</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16315</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23106</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>73,54%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>59,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>84,96%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25071</t>
+          <t>20325</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20240</t>
+          <t>16531</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29395</t>
+          <t>23417</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>45069</t>
+          <t>43712</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38823</t>
+          <t>37200</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50711</t>
+          <t>48756</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>80,98%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9085</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13650</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>27,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,15%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,03%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7197</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4089</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10880</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>26,46%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,04%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>40,01%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>11205</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>17359</t>
+          <t>16496</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11717</t>
+          <t>11452</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23605</t>
+          <t>23008</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,21%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>32472</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>32472</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>32472</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>27195</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>27195</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>27195</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35233</t>
+          <t>27736</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35233</t>
+          <t>27736</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35233</t>
+          <t>27736</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>62428</t>
+          <t>60208</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62428</t>
+          <t>60208</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>62428</t>
+          <t>60208</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>51704</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>46555</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>55421</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>87,94%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>79,19%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>94,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>30488</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>25147</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>34876</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>77,55%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>63,96%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>88,71%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>55154</t>
+          <t>30512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49060</t>
+          <t>24296</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58798</t>
+          <t>34587</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>85643</t>
+          <t>82216</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77902</t>
+          <t>73720</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91192</t>
+          <t>87682</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,33%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7088</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3371</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12237</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>12,06%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20,81%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>8826</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4438</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14167</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>22,45%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36,04%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13460</t>
+          <t>15068</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>16191</t>
+          <t>15940</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23932</t>
+          <t>24436</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>58792</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>58792</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>58792</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>39314</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>39314</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>39314</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62520</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62520</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62520</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>101834</t>
+          <t>98156</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>101834</t>
+          <t>98156</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>101834</t>
+          <t>98156</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28561</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22493</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33513</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>68,81%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>54,19%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>80,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>20237</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15481</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24541</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>66,96%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>51,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>81,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30112</t>
+          <t>17364</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23156</t>
+          <t>13091</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35021</t>
+          <t>21502</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>50348</t>
+          <t>45925</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42944</t>
+          <t>38806</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57179</t>
+          <t>51819</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>75,34%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12946</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7994</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19014</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>31,19%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>45,81%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>9984</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5680</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>14740</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>33,04%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>18,79%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>48,77%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14076</t>
+          <t>9913</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9167</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21032</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>24061</t>
+          <t>22859</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17230</t>
+          <t>16965</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31465</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>43,58%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>41507</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41507</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>41507</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>30221</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>30221</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>30221</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>27277</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>27277</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>27277</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>74409</t>
+          <t>68784</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>74409</t>
+          <t>68784</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>74409</t>
+          <t>68784</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32515</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26379</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>37399</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>71,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>57,86%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>82,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>32182</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>26117</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>36830</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>69,41%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>56,33%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>79,44%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36111</t>
+          <t>31195</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29209</t>
+          <t>25323</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41106</t>
+          <t>35594</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>68293</t>
+          <t>63710</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59941</t>
+          <t>55459</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75444</t>
+          <t>70677</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>77,88%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13079</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8195</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>19215</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>28,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>17,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>42,14%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>14182</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9534</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20247</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>30,59%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20,56%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>43,67%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13718</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>9563</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20620</t>
+          <t>19834</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>27900</t>
+          <t>27041</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20749</t>
+          <t>20074</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36252</t>
+          <t>35292</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>38,89%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>45594</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>45594</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>45594</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>46364</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>46364</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>46364</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>45157</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>45157</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>45157</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>96193</t>
+          <t>90751</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>96193</t>
+          <t>90751</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>96193</t>
+          <t>90751</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>136167</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>126085</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>145254</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>76,34%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>70,69%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>81,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>102905</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>93844</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>111272</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>71,91%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>65,58%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>77,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>146448</t>
+          <t>99396</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>134765</t>
+          <t>89886</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>157301</t>
+          <t>107975</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>249353</t>
+          <t>235563</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>236071</t>
+          <t>221415</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>263118</t>
+          <t>248795</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,26%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>42198</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>33111</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>52280</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>23,66%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>18,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29,31%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>40188</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>31821</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>49249</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>28,09%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>22,24%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>34,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>45322</t>
+          <t>40138</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34469</t>
+          <t>31559</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57005</t>
+          <t>49648</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>85510</t>
+          <t>82336</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71745</t>
+          <t>69104</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>98792</t>
+          <t>96484</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>143093</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>143093</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>143093</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>334863</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>334863</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>334863</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
